--- a/data/trans_orig/P6710-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2012</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2012 (tasa de respuesta: 98,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40590</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26214</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32722</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58116</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>14288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53194</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50597</t>
+          <t>49962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81539</t>
+          <t>80788</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>62544</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>39639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>64754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>97161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117116</t>
+          <t>117122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149036</t>
+          <t>150116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57867</t>
+          <t>58631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83951</t>
+          <t>84020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184351</t>
+          <t>181809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>225342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>33765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58403</t>
+          <t>61275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>40079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54755</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89628</t>
+          <t>90187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43737</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>26395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62366</t>
+          <t>62789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68671</t>
+          <t>66995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102981</t>
+          <t>100530</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35195</t>
+          <t>34131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60794</t>
+          <t>59926</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107998</t>
+          <t>108871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152104</t>
+          <t>152481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69625</t>
+          <t>71316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>105351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80956</t>
+          <t>80777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132641</t>
+          <t>132119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177536</t>
+          <t>177944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144344</t>
+          <t>143759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184599</t>
+          <t>186080</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95173</t>
+          <t>95128</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128088</t>
+          <t>126765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>245881</t>
+          <t>250623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298393</t>
+          <t>303746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40590</t>
+          <t>41233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>41666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44297</t>
+          <t>45799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>77094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32064</t>
+          <t>31028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27436</t>
+          <t>27694</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53452</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60423</t>
+          <t>59311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90396</t>
+          <t>91479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49343</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89752</t>
+          <t>91612</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129894</t>
+          <t>133495</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>40354</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66384</t>
+          <t>66709</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>29553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53192</t>
+          <t>53399</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74552</t>
+          <t>76218</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111882</t>
+          <t>112127</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123042</t>
+          <t>123958</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160499</t>
+          <t>160250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69869</t>
+          <t>69125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100333</t>
+          <t>98778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202124</t>
+          <t>204192</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250781</t>
+          <t>250616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,58%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50763</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>35452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61844</t>
+          <t>63554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69177</t>
+          <t>70304</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104550</t>
+          <t>107556</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>27835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54433</t>
+          <t>54216</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29000</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52413</t>
+          <t>52128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61751</t>
+          <t>63350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97261</t>
+          <t>99439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83035</t>
+          <t>84168</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118827</t>
+          <t>120162</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>53112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81876</t>
+          <t>81152</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>145096</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>190856</t>
+          <t>192245</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93817</t>
+          <t>94955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131389</t>
+          <t>131014</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41003</t>
+          <t>41567</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>68831</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142667</t>
+          <t>145250</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188505</t>
+          <t>192041</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>106167</t>
+          <t>105094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145350</t>
+          <t>143920</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78447</t>
+          <t>77344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111348</t>
+          <t>111001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>194597</t>
+          <t>192300</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244871</t>
+          <t>244372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114556</t>
+          <t>114738</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>162582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100649</t>
+          <t>103443</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143729</t>
+          <t>145822</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>232853</t>
+          <t>231854</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>298284</t>
+          <t>293419</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>92123</t>
+          <t>90642</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135760</t>
+          <t>135581</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>72394</t>
+          <t>74131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>112893</t>
+          <t>112108</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>175147</t>
+          <t>176266</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>231292</t>
+          <t>234070</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>263089</t>
+          <t>265133</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>323334</t>
+          <t>325211</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>153510</t>
+          <t>152244</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>202693</t>
+          <t>203388</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>432261</t>
+          <t>433235</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>511929</t>
+          <t>515575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>272158</t>
+          <t>269276</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>335218</t>
+          <t>333028</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>164464</t>
+          <t>162389</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>214331</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>451391</t>
+          <t>449582</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>533910</t>
+          <t>533129</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>525311</t>
+          <t>529498</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>597471</t>
+          <t>602581</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>333239</t>
+          <t>333069</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>391467</t>
+          <t>393339</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>879634</t>
+          <t>876157</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>977402</t>
+          <t>973936</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2016</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45569</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18398</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>34796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45575</t>
+          <t>44326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73041</t>
+          <t>73134</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39591</t>
+          <t>39680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17302</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>41904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68580</t>
+          <t>69120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42711</t>
+          <t>41590</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68337</t>
+          <t>67327</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>32190</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54848</t>
+          <t>54139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80362</t>
+          <t>80634</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>115048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47474</t>
+          <t>49593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75814</t>
+          <t>77580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45724</t>
+          <t>44604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79882</t>
+          <t>79119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112726</t>
+          <t>113314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>53366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80969</t>
+          <t>80996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50309</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87937</t>
+          <t>88798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123266</t>
+          <t>123768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38726</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>66791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>41924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66119</t>
+          <t>68179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102828</t>
+          <t>104984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>44755</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>75401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>37545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61585</t>
+          <t>62341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89924</t>
+          <t>88737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129854</t>
+          <t>129016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>81823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116242</t>
+          <t>116214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55400</t>
+          <t>55427</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83695</t>
+          <t>83833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144790</t>
+          <t>142776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189671</t>
+          <t>190061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80974</t>
+          <t>83052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118746</t>
+          <t>121351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47539</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75985</t>
+          <t>77314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138263</t>
+          <t>139187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183580</t>
+          <t>186867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86716</t>
+          <t>87395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122000</t>
+          <t>124513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50956</t>
+          <t>50205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79395</t>
+          <t>80419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146067</t>
+          <t>146532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191115</t>
+          <t>192353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33986</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61556</t>
+          <t>61604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>62307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>98888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62638</t>
+          <t>64037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94128</t>
+          <t>97543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52609</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78929</t>
+          <t>79643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122714</t>
+          <t>124052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>166699</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94769</t>
+          <t>94332</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130501</t>
+          <t>131483</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64623</t>
+          <t>63116</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93290</t>
+          <t>92408</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>167471</t>
+          <t>167080</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>213833</t>
+          <t>214510</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>44374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75351</t>
+          <t>74852</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49715</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77552</t>
+          <t>79036</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115274</t>
+          <t>116010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>53792</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82503</t>
+          <t>85829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>45240</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73139</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106629</t>
+          <t>106280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149250</t>
+          <t>147505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39662</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65699</t>
+          <t>66838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51757</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81272</t>
+          <t>79899</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98244</t>
+          <t>96956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140154</t>
+          <t>137358</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44371</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71797</t>
+          <t>71410</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>67328</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90579</t>
+          <t>90301</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127746</t>
+          <t>127871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83943</t>
+          <t>83513</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118939</t>
+          <t>117571</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62007</t>
+          <t>60738</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93177</t>
+          <t>92988</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>154228</t>
+          <t>153386</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202255</t>
+          <t>199769</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61085</t>
+          <t>61161</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>94536</t>
+          <t>92448</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45808</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74457</t>
+          <t>74162</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117103</t>
+          <t>115675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156495</t>
+          <t>159921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98179</t>
+          <t>98196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134079</t>
+          <t>134583</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91241</t>
+          <t>89761</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>167135</t>
+          <t>165961</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213317</t>
+          <t>213882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156014</t>
+          <t>156755</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209125</t>
+          <t>207443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135678</t>
+          <t>134522</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>179859</t>
+          <t>182724</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>304203</t>
+          <t>307370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>372554</t>
+          <t>377543</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>199302</t>
+          <t>197332</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>253631</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>161851</t>
+          <t>166869</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>213099</t>
+          <t>215976</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>375103</t>
+          <t>379011</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>447793</t>
+          <t>454149</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>330543</t>
+          <t>332339</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>396966</t>
+          <t>397845</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>236071</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>291371</t>
+          <t>294530</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>587163</t>
+          <t>588022</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>674244</t>
+          <t>675725</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>268041</t>
+          <t>268688</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>330344</t>
+          <t>329628</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>166721</t>
+          <t>166734</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>216769</t>
+          <t>217675</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>451734</t>
+          <t>449150</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>530621</t>
+          <t>530009</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>324521</t>
+          <t>321071</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>390279</t>
+          <t>389656</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>211355</t>
+          <t>208464</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>263673</t>
+          <t>262282</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>548870</t>
+          <t>545625</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>635214</t>
+          <t>635364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/P6710-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>18819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41443</t>
+          <t>39244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>59099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35037</t>
+          <t>33434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>25258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52506</t>
+          <t>51356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>46986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>39866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49962</t>
+          <t>50278</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80788</t>
+          <t>82882</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62544</t>
+          <t>61963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39639</t>
+          <t>39876</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64754</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97161</t>
+          <t>95902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117122</t>
+          <t>115781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150116</t>
+          <t>149389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58631</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84020</t>
+          <t>84939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181809</t>
+          <t>182608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>225342</t>
+          <t>225890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61275</t>
+          <t>57853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40079</t>
+          <t>39282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>56554</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90187</t>
+          <t>92193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35167</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62789</t>
+          <t>60525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66995</t>
+          <t>66794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100530</t>
+          <t>102055</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>35598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59926</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108871</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152481</t>
+          <t>150731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71316</t>
+          <t>71182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>105907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>51458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80777</t>
+          <t>81726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132119</t>
+          <t>132570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177944</t>
+          <t>176290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143759</t>
+          <t>143999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186080</t>
+          <t>183682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95128</t>
+          <t>94466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126765</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250623</t>
+          <t>251522</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303746</t>
+          <t>301420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41233</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>21049</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41666</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45799</t>
+          <t>46357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77094</t>
+          <t>76847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30047</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27694</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>54085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59311</t>
+          <t>58188</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91479</t>
+          <t>91569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49427</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91612</t>
+          <t>91519</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133495</t>
+          <t>131411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40354</t>
+          <t>39051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66709</t>
+          <t>64772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29553</t>
+          <t>29038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53399</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76218</t>
+          <t>75466</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112127</t>
+          <t>112040</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>122341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160250</t>
+          <t>159476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69125</t>
+          <t>70483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98778</t>
+          <t>100645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204192</t>
+          <t>202184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250616</t>
+          <t>251389</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27150</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>52518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63554</t>
+          <t>61303</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70304</t>
+          <t>68504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107556</t>
+          <t>103560</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54216</t>
+          <t>54325</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52128</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63350</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99439</t>
+          <t>97555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84168</t>
+          <t>85120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120162</t>
+          <t>118831</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53112</t>
+          <t>52564</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81152</t>
+          <t>81316</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>143391</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192245</t>
+          <t>190321</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94955</t>
+          <t>95353</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131014</t>
+          <t>130813</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>41167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68831</t>
+          <t>67639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145250</t>
+          <t>145804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192041</t>
+          <t>190725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105094</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143920</t>
+          <t>141816</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77344</t>
+          <t>77353</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>111045</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>192300</t>
+          <t>192211</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244372</t>
+          <t>243310</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114738</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>162582</t>
+          <t>163242</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>102976</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>145822</t>
+          <t>142747</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>231854</t>
+          <t>230016</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>293419</t>
+          <t>295208</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90642</t>
+          <t>92345</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135581</t>
+          <t>134757</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74131</t>
+          <t>74576</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>112108</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>176266</t>
+          <t>175011</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>234070</t>
+          <t>233128</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>265133</t>
+          <t>261695</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>325211</t>
+          <t>323087</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152244</t>
+          <t>154541</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>203388</t>
+          <t>202533</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>433235</t>
+          <t>429307</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>515575</t>
+          <t>514697</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>269276</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>333028</t>
+          <t>334641</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>162389</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>211832</t>
+          <t>216078</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>449582</t>
+          <t>452735</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>533129</t>
+          <t>531013</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>529498</t>
+          <t>525793</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>602581</t>
+          <t>599413</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>333069</t>
+          <t>331589</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>393339</t>
+          <t>392868</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>876157</t>
+          <t>878083</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>973936</t>
+          <t>978907</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>43805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17318</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44326</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73134</t>
+          <t>72790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>35727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41904</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69120</t>
+          <t>68622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41590</t>
+          <t>41950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67327</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32190</t>
+          <t>31831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54139</t>
+          <t>53137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80634</t>
+          <t>79683</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115048</t>
+          <t>114709</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49593</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77580</t>
+          <t>76651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>45686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79119</t>
+          <t>79325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113314</t>
+          <t>114152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53366</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80996</t>
+          <t>81353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50933</t>
+          <t>50438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88798</t>
+          <t>88591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123768</t>
+          <t>124897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66791</t>
+          <t>67213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41924</t>
+          <t>42577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>65770</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104984</t>
+          <t>101128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44755</t>
+          <t>45260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75401</t>
+          <t>75722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62341</t>
+          <t>61672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88737</t>
+          <t>89162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129016</t>
+          <t>127506</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81823</t>
+          <t>80931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116214</t>
+          <t>118614</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55427</t>
+          <t>53165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83833</t>
+          <t>82345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142776</t>
+          <t>144742</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>190061</t>
+          <t>193007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83052</t>
+          <t>81803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121351</t>
+          <t>118509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>48409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77314</t>
+          <t>75737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139187</t>
+          <t>138839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186867</t>
+          <t>186061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>87269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124513</t>
+          <t>123658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50205</t>
+          <t>50484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80419</t>
+          <t>81592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146532</t>
+          <t>145660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192353</t>
+          <t>194590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>32721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61604</t>
+          <t>60698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>23349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45739</t>
+          <t>45208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62307</t>
+          <t>64963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98888</t>
+          <t>98074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64037</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97543</t>
+          <t>96770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53115</t>
+          <t>51954</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79643</t>
+          <t>79587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124052</t>
+          <t>121957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>166699</t>
+          <t>168820</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94332</t>
+          <t>94027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131483</t>
+          <t>130658</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>62735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>91598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>167080</t>
+          <t>166756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>214510</t>
+          <t>213906</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44374</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74852</t>
+          <t>75620</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>27235</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79036</t>
+          <t>78279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116010</t>
+          <t>116654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53792</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85829</t>
+          <t>85008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45240</t>
+          <t>45450</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72727</t>
+          <t>72682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106280</t>
+          <t>107457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147505</t>
+          <t>147393</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39543</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66838</t>
+          <t>66020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>51077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79899</t>
+          <t>81481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96956</t>
+          <t>99111</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137358</t>
+          <t>139252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44752</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>71304</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>36895</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>62660</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90301</t>
+          <t>90309</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127871</t>
+          <t>129141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83513</t>
+          <t>84048</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117571</t>
+          <t>119385</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60738</t>
+          <t>61662</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>92988</t>
+          <t>91608</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>153386</t>
+          <t>154758</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>199769</t>
+          <t>199545</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61161</t>
+          <t>62782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92448</t>
+          <t>93680</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>46355</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74162</t>
+          <t>74164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115675</t>
+          <t>116028</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159921</t>
+          <t>158488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98196</t>
+          <t>98571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134583</t>
+          <t>134856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60027</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>90265</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>165961</t>
+          <t>168455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>213882</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156755</t>
+          <t>155977</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207443</t>
+          <t>209313</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134522</t>
+          <t>134300</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182724</t>
+          <t>180331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>307370</t>
+          <t>306972</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>377543</t>
+          <t>373003</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>197332</t>
+          <t>195696</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>252340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>166869</t>
+          <t>165494</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>215976</t>
+          <t>212940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>379011</t>
+          <t>379810</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>454149</t>
+          <t>456150</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>332339</t>
+          <t>331834</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>397845</t>
+          <t>400174</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>237273</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>294530</t>
+          <t>292631</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>588022</t>
+          <t>584437</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>675725</t>
+          <t>670724</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>268688</t>
+          <t>267259</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>329628</t>
+          <t>328269</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>166734</t>
+          <t>169858</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>217675</t>
+          <t>217528</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>449150</t>
+          <t>449467</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>530009</t>
+          <t>528774</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>321071</t>
+          <t>323428</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>389656</t>
+          <t>393283</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>208464</t>
+          <t>208440</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>262282</t>
+          <t>263212</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>545625</t>
+          <t>545488</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>635364</t>
+          <t>636334</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
